--- a/04_meeting_documents/meeting_document_metadata.xlsx
+++ b/04_meeting_documents/meeting_document_metadata.xlsx
@@ -663,7 +663,7 @@
         <x:v>제품 기획</x:v>
       </x:c>
       <x:c r="F2" s="5" t="str">
-        <x:v>신규기능_리뷰_0924.png</x:v>
+        <x:v>신규기능_리뷰_0924.jpg</x:v>
       </x:c>
       <x:c r="G2" s="5" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -689,7 +689,7 @@
         <x:v>UX 리서치</x:v>
       </x:c>
       <x:c r="F3" s="2" t="str">
-        <x:v>사용성테스트_요약.png</x:v>
+        <x:v>사용성테스트_요약.jpg</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -715,7 +715,7 @@
         <x:v>개발</x:v>
       </x:c>
       <x:c r="F4" s="5" t="str">
-        <x:v>기능별_일정표_v2.png</x:v>
+        <x:v>기능별_일정표_v2.jpg</x:v>
       </x:c>
       <x:c r="G4" s="5" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -741,7 +741,7 @@
         <x:v>예산 담당</x:v>
       </x:c>
       <x:c r="F5" s="2" t="str">
-        <x:v>4분기_예산안_v4.png</x:v>
+        <x:v>4분기_예산안_v4.jpg</x:v>
       </x:c>
       <x:c r="G5" s="2" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -767,7 +767,7 @@
         <x:v>예산 담당</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
-        <x:v>상반기_집행실적.png</x:v>
+        <x:v>상반기_집행실적.jpg</x:v>
       </x:c>
       <x:c r="G6" s="5" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -793,7 +793,7 @@
         <x:v>회의 진행</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
-        <x:v>예산_심의의견_취합.png</x:v>
+        <x:v>예산_심의의견_취합.jpg</x:v>
       </x:c>
       <x:c r="G7" s="2" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -819,7 +819,7 @@
         <x:v>UX 디자인</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>메인화면_시안_A안.png</x:v>
+        <x:v>메인화면_시안_A안.jpg</x:v>
       </x:c>
       <x:c r="G8" s="5" t="str">
         <x:v>선택한 회의의 검색결과</x:v>
@@ -845,7 +845,7 @@
         <x:v>UX 디자인</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
-        <x:v>시안_설명자료.png</x:v>
+        <x:v>시안_설명자료.jpg</x:v>
       </x:c>
       <x:c r="G9" s="2" t="str">
         <x:v>선택한 회의의 검색결과</x:v>

--- a/04_meeting_documents/meeting_document_metadata.xlsx
+++ b/04_meeting_documents/meeting_document_metadata.xlsx
@@ -397,13 +397,13 @@
         <x:v>xlsx</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>M20260917</x:v>
+        <x:v>M20260922</x:v>
       </x:c>
       <x:c r="D5" s="2" t="str">
         <x:v>분기 예산 회의</x:v>
       </x:c>
       <x:c r="E5" s="7" t="n">
-        <x:v>46282.42013888889</x:v>
+        <x:v>46287.42013888889</x:v>
       </x:c>
       <x:c r="F5" s="2" t="str">
         <x:v>예산, 4분기, 심의안</x:v>
@@ -420,13 +420,13 @@
         <x:v>pdf</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>M20260917</x:v>
+        <x:v>M20260922</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>분기 예산 회의</x:v>
       </x:c>
       <x:c r="E6" s="6" t="n">
-        <x:v>46282.42708333333</x:v>
+        <x:v>46287.42708333333</x:v>
       </x:c>
       <x:c r="F6" s="5" t="str">
         <x:v>집행실적, 상반기, 예산</x:v>
@@ -443,13 +443,13 @@
         <x:v>docx</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>M20260917</x:v>
+        <x:v>M20260922</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
         <x:v>분기 예산 회의</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>46282.45</x:v>
+        <x:v>46287.45</x:v>
       </x:c>
       <x:c r="F7" s="2" t="str">
         <x:v>심의 의견, 예산, 후속 조치</x:v>
@@ -466,13 +466,13 @@
         <x:v>pdf</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>M20260911</x:v>
+        <x:v>M20260921</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>디자인 시안 공유</x:v>
       </x:c>
       <x:c r="E8" s="6" t="n">
-        <x:v>46276.425</x:v>
+        <x:v>46286.425</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
         <x:v>메인화면, A안, 디자인</x:v>
@@ -489,13 +489,13 @@
         <x:v>pptx</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
-        <x:v>M20260911</x:v>
+        <x:v>M20260921</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
         <x:v>디자인 시안 공유</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>46276.44097222222</x:v>
+        <x:v>46286.44097222222</x:v>
       </x:c>
       <x:c r="F9" s="2" t="str">
         <x:v>시안, 설명, 디자인</x:v>
@@ -563,16 +563,16 @@
     </x:row>
     <x:row r="3" ht="44" customHeight="1">
       <x:c r="A3" s="2" t="str">
-        <x:v>M20260917</x:v>
+        <x:v>M20260922</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
         <x:v>분기 예산 회의</x:v>
       </x:c>
       <x:c r="C3" s="7" t="n">
-        <x:v>46282.41666666667</x:v>
+        <x:v>46287.41666666667</x:v>
       </x:c>
       <x:c r="D3" s="7" t="n">
-        <x:v>46282.45833333333</x:v>
+        <x:v>46287.45833333333</x:v>
       </x:c>
       <x:c r="E3" s="2" t="str">
         <x:v>회의실 B</x:v>
@@ -583,16 +583,16 @@
     </x:row>
     <x:row r="4" ht="44" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>M20260911</x:v>
+        <x:v>M20260921</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>디자인 시안 공유</x:v>
       </x:c>
       <x:c r="C4" s="6" t="n">
-        <x:v>46276.41666666667</x:v>
+        <x:v>46286.41666666667</x:v>
       </x:c>
       <x:c r="D4" s="6" t="n">
-        <x:v>46276.45833333333</x:v>
+        <x:v>46286.45833333333</x:v>
       </x:c>
       <x:c r="E4" s="5" t="str">
         <x:v>온라인 회의</x:v>
@@ -729,7 +729,7 @@
         <x:v>4분기_예산안_v4.xlsx</x:v>
       </x:c>
       <x:c r="B5" s="7" t="n">
-        <x:v>46282.41666666667</x:v>
+        <x:v>46287.41666666667</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
         <x:v>Asia/Seoul</x:v>
@@ -755,7 +755,7 @@
         <x:v>상반기_집행실적.pdf</x:v>
       </x:c>
       <x:c r="B6" s="6" t="n">
-        <x:v>46282.41666666667</x:v>
+        <x:v>46287.41666666667</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>Asia/Seoul</x:v>
@@ -781,7 +781,7 @@
         <x:v>예산_심의의견_취합.docx</x:v>
       </x:c>
       <x:c r="B7" s="7" t="n">
-        <x:v>46282.41666666667</x:v>
+        <x:v>46287.41666666667</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
         <x:v>Asia/Seoul</x:v>
@@ -807,7 +807,7 @@
         <x:v>메인화면_시안_A안.pdf</x:v>
       </x:c>
       <x:c r="B8" s="6" t="n">
-        <x:v>46276.41666666667</x:v>
+        <x:v>46286.41666666667</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>Asia/Seoul</x:v>
@@ -833,7 +833,7 @@
         <x:v>시안_설명자료.pptx</x:v>
       </x:c>
       <x:c r="B9" s="7" t="n">
-        <x:v>46276.41666666667</x:v>
+        <x:v>46286.41666666667</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
         <x:v>Asia/Seoul</x:v>
